--- a/신고신저가_20260811.xlsx
+++ b/신고신저가_20260811.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,18 +77,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,64 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 호르무즈 봉쇄 장기화로 유가 급등(브렌트 87달러대, +5%) — 지수는 인플레 우려로 눌리는데 신고가는 보안SW·바이오·금광으로 쏠리는 테마 분화 국면. 8/12 미 CPI 대기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/10): 나스닥 -0.32%·S&amp;P500 -0.06%·다우 -0.11%. XLE +4.7%로 전 섹터 최강, 반대편 XLRE -1.3%·XLU -1.1%·XLK -0.9%. 신고 76(NEW 36)은 Technology Services 22/0(순강도 +22, 12MF PER 23.4)·Health Technology 18/1(19.1)에 집중 — 팔로알토 +5.8%·크라우드스트라이크 +5.0%(AI에이전트 자율해킹 보도로 보안주 랠리), 버텍스 +5.6%(비마약성 진통제 3상), 벤딩스푼스 +15.7%(에어테이블 12.8억달러 인수). 신저 16 중 6종이 유틸리티(AEP·DTE), 알트리아·리츠가 뒤를 이음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/10): 1분기 결산 랠리 지속 — 정보통신·서비스 ETF +3.6%·철강비철 +3.4%·전기정밀 +2.0%. 리크루트 +22.8%(연간 영업이익 7870억→9450억엔 상향), 올림푸스 +10.1%(영업이익 74%↑)·니토리 +9.7%·테루모 +8.5% 모두 1분기 서프라이즈. 약세는 부동산 -2.5%·전력가스 -2.2%·은행 -1.9%로 금리·경기 민감주 쪽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 中·홍콩(8/11): 항셍 -0.61%·항셍테크 -1.27%·상해종합 -0.05%·CSI300 +0.15%. 양쪽 다 신저가 0종으로 하방은 잠잠. 신고가 명단은 금광 편중 — 츠펑지룽(A·H 동시)·중진황금·산진국제황금·중국황금국제가 국제 금값 고공권을 반영하나 당일은 -1~-2.6% 차익실현. A주 ETF는 의약 +1.2%·5G +1.1%·테크 +1.0% 강세, 유색금속 -1.4%·소비 -1.4% 약세. 홍콩은 캉룽화청 +9.3%로 CXO 랠리 연장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①8/12 미 CPI — 유가발 인플레가 헤드라인에 얼마나 실리는지 ②봉쇄 지속 시 에너지주 신고가 등장 여부(XLE +4.7%인데 Energy Minerals 순강도 0으로 아직 없음) ③미 유틸리티 신저 6종이 이틀 연속 — 금리 방향과 무관하게 반복되는 구조 요인인지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 美·日은 2026-08-10(월) 마감 확정치이며 美는 한국시간 8/11 새벽 마감분. 일본은 8/11 산의 날 휴장이라 8/10 기준이고, 닛케이 지수 등락은 소스 미확보로 섹터ETF 기준으로만 기술. 홍콩·중국A는 8/11 오전장 스냅샷(한국시간 13시경 실행)이라 마감 확정치 아님. 오늘 실행이 정시(07:30)보다 늦어 미장 마감 후 8시간 시점 데이터.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +771,19 @@
       <c r="C2" t="n">
         <v>7753.11</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.06</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>2.01</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>2.35</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>4.79</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>13.26</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +809,19 @@
       <c r="C3" t="n">
         <v>26605.36</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-0.32</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>2.67</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>1.23</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>1.37</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>14.47</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +847,19 @@
       <c r="C4" t="n">
         <v>6367.46</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>1.08</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>0.13</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>-14.83</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-18.6</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>51.1</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +885,19 @@
       <c r="C5" t="n">
         <v>66970.22</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>2.08</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>5.04</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>-1.14</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>6.74</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>33.04</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +923,19 @@
       <c r="C6" t="n">
         <v>3964.79</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>-0.05</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>3.73</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-6.55</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>-0.1</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +961,19 @@
       <c r="C7" t="n">
         <v>4709.1</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>2.35</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>0.29</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-5.79</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>1.71</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +999,19 @@
       <c r="C8" t="n">
         <v>25773.56</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>-0.63</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>-0.31</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>6.44</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1037,19 @@
       <c r="C9" t="n">
         <v>4857.12</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>-1.27</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>-0.58</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>3.86</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-4.88</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-11.94</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1168,7 @@
       <c r="F2" t="n">
         <v>22</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1209,7 @@
       <c r="F3" t="n">
         <v>17</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1250,7 @@
       <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1291,7 @@
       <c r="F5" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1332,7 @@
       <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1373,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1414,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1455,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1496,7 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1537,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1578,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1619,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1660,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1701,7 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1678,7 +1740,7 @@
       <c r="F16" t="n">
         <v>-2</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1719,7 +1781,7 @@
       <c r="F17" t="n">
         <v>-6</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1986,7 @@
       <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2027,7 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2066,7 @@
       <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2043,7 +2105,7 @@
       <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2084,7 +2146,7 @@
       <c r="F26" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2125,7 +2187,7 @@
       <c r="F27" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2164,7 +2226,7 @@
       <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2203,7 +2265,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2242,7 +2304,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2281,7 +2343,7 @@
       <c r="F31" t="n">
         <v>-1</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2320,7 +2382,7 @@
       <c r="F32" t="n">
         <v>-1</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2675,7 +2737,7 @@
       <c r="F41" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2716,7 +2778,7 @@
       <c r="F42" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2755,7 +2817,7 @@
       <c r="F43" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2796,7 +2858,7 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2837,7 +2899,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2878,7 +2940,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3397,7 +3459,7 @@
       <c r="F59" t="n">
         <v>3</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3436,7 +3498,7 @@
       <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3477,7 +3539,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3518,7 +3580,7 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -4101,30 +4163,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4208,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4318,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.9%지만 SW·보안 신고가 22종(순강도 +22, 12MF 23.4) — 하락은 반도체·하드웨어 몫 추정</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4394,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.7%·3M +17.9%로 모멘텀 최상위. Health Technology 신고18/신저1, 버텍스·바이오마린 주도</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4470,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.4%, Finance 신고10/신저3(12MF 15.2). IB는 에버코어가 신저로 갈림</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4546,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.2% 보합. Retail Trade 신고3으로 온기는 남았으나 유가 급등이 소비 심리 부담 추정</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4622,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.5%, 신고·신저 0종. YTD -4.5%로 올해 미국 최약 섹터 지위 유지</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4698,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.3%, Producer Manufacturing 신고1/신저1 혼조·Industrial Services 순강도 -2</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4774,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.2%, 알트리아가 신저(2분기 부진 여파). 방어주 프리미엄 소멸 구간</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4850,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>1D +4.7%로 전 섹터 최강 — 호르무즈 봉쇄 장기화에 브렌트 87달러대. YTD +36.5%</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>36.5</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4926,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.1%·1M -5.0%, 신저 6종으로 최다. 유가발 인플레·금리 부담 추정</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5002,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.6%·1주 +4.3%, Non-Energy Minerals 신고5/신저1 — 금·구리 등 광물 강세 반영</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5078,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.3%로 하루 최약, GLPI 신저. 인플레 재점화가 리츠 밸류에이션 압박 추정</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5154,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5226,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-7</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5298,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-6.5</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-10.5</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5370,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5442,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>12</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5514,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5586,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>13.6</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>51.7</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5658,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>7</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5730,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>9.5</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>35.5</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5802,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>13.6</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5874,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5946,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>14</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6018,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6090,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>13</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6162,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>43.1</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6234,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6306,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-12.4</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6378,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6450,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9" t="n">
         <v>6.2</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6522,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-11.7</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6590,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>오전장 +0.8%·1주 +12.5%로 반등 지속, 다만 1M -15.6%로 낙폭 회복은 초입</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-15.6</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>48.9</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6666,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>오전장 +1.0%·1주 +7.4%, 성장주 반등 동참하나 1M -9.3%로 아직 마이너스</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>33.5</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6742,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>오전장 +1.1%로 A주 상위권, 1M -11.1%·3M -10.9%의 조정 되돌림 성격</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-11.1</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-10.9</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>35.7</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6818,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>오전장 -0.1% 보합, 3M -20.2%로 부진 지속 — 반등 신호 미확인</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-20.2</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-10.3</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6890,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>오전장 -1.2%, 3M -22.2%로 A주 최악권. 방산 소외 지속</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-22.2</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6966,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>오전장 +0.9%, 다만 3M -24.1%로 13개 중 최대 낙폭 — 추세 전환 근거 부족</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-24.1</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-9.6</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7038,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>오전장 -1.1%지만 1M +12.0%로 중기 반등은 유지. 소비 회복 기대 되돌림 추정</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-17.9</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>12</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7114,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>오전장 -0.4%, Finance 12MF PER 6.0(표본 9종)의 저평가 방어주 성격 유지</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7190,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>오전장 -1.4%지만 1M +18.5%로 최강 — 금광주 신고가 3종 나오고 당일은 차익실현</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7266,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>오전장 +0.2% 보합, 3M -17.5%·YTD -17.9%로 부동산 소외 지속</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-17.5</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-17.9</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>12</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7342,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>오전장 0.0% 무변동, 1M +0.1%로 거래대금 모멘텀 부재 — 지수 방향 대기</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7418,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>오전장 +1.2%로 A주 최강, 1M +13.9%·3M +10.8%. Health Technology 신고2·홍콩 CXO 랠리와 연결</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7494,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>오전장 -1.4%로 최약, 1M +7.8%는 유지. 유가 급등발 소비 부담 추정</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7562,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-2.5"/>
@@ -7366,7 +7574,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-2.8"/>
@@ -7378,7 +7586,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-15.6"/>
@@ -7390,7 +7598,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-24.1"/>
@@ -7402,7 +7610,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-17.9"/>
@@ -7414,7 +7622,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7634,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7646,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7658,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7670,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7682,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,7 +7796,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7637,15 +7845,15 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7693,15 +7901,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7749,15 +7957,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7805,10 +8013,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7857,15 +8065,15 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7913,15 +8121,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>팔로알토네트웍스(기업 보안SW): 오펜하이머·바클레이스 목표가 상향+AI에이전트 해킹 보도로 보안주 랠리</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7969,15 +8181,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8023,10 +8235,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>크라우드스트라이크(클라우드 엔드포인트 보안): AI에이전트 자율 해킹 사건 보도에 보안주 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8075,15 +8291,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8127,15 +8343,15 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8183,15 +8399,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8235,15 +8451,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8287,15 +8503,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8339,10 +8555,10 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8391,15 +8607,15 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8443,15 +8659,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8499,10 +8715,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>버텍스파마(희귀질환·통증 신약): 비마약성 진통제 3상 톱라인 데이터 긍정 발표</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8553,15 +8773,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8605,10 +8825,10 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8657,14 +8877,14 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>(전일) 엔브리지(캐나다 에너지 파이프라인): 개별 뉴스 없음, 에너지 섹터 약세(추정)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8717,19 +8937,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>(전일) 에어비앤비(숙박공유 플랫폼): 2분기 서프라이즈·GBV 16%↑, 3분기·연간 매출 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8771,10 +8991,14 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>알트리아(미국 담배): 7월말 2분기 부진·가이던스 하향 여파 지속, 고배당주 소외</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8823,10 +9047,10 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8875,15 +9099,15 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8927,15 +9151,15 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8983,15 +9207,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9031,10 +9255,14 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>아메리칸일렉트릭파워(전력 유틸리티): 8/10 배당락일, 유틸리티 섹터 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9083,10 +9311,10 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9139,10 +9367,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9195,10 +9423,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9247,10 +9475,10 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9299,15 +9527,15 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9351,10 +9579,10 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9403,14 +9631,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="7" t="inlineStr">
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>(전일) 나테라(암·유전자 진단검사): 2분기 매출 컨센 대폭 상회, 연간 가이던스 상향·검사량 기록</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9459,10 +9687,10 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9511,10 +9739,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9563,10 +9791,10 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9615,15 +9843,15 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9671,10 +9899,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="7" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>넷앱(엔터프라이즈 스토리지): 단일 촉매 미확인, AI인프라 스토리지 수혜 기대·투자의견 상향 여진</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9719,14 +9951,14 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>(전일) 아틀라시안(협업SW Jira·Confluence): 2분기 매출 28%↑·클라우드 31% 가속, Rovo AI 견인</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9775,10 +10007,10 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9831,14 +10063,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>(전일) 트윌로(클라우드 통신API): 2분기 매출·EPS 서프라이즈, 3분기 가이던스·FCF 전망 상향</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9887,10 +10119,10 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9939,19 +10171,19 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>(전일) WEC에너지(위스콘신 전력·가스): 특별한 뉴스 없음, 유틸리티 섹터 소외 흐름 추정</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9993,15 +10225,15 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10049,15 +10281,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N47" s="7" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10105,15 +10337,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10157,10 +10389,10 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10211,19 +10443,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 벤딩스푼스(앱 인수·운영 이탈리아 테크): +16.8% 급등, 촉매 미확인(상장 초기 변동성 추정)</t>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>벤딩스푼스(앱 인수·운영, 이탈리아): 에어테이블 12.8억달러 인수 발표, 8/13 2분기 실적 앞두고 강세</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10271,15 +10503,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>에버퓨어(올플래시 데이터 스토리지): 서스퀘하나 투자의견 상향, AI·클라우드 플래시 수요 부각</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10327,10 +10563,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N52" s="7" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10379,15 +10615,15 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10435,15 +10671,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10491,15 +10727,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10543,15 +10779,15 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10595,10 +10831,14 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>DTE에너지(미시간 전력·가스): 특별한 뉴스 없음, 유틸리티 섹터 동반 약세(금리 부담 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10649,15 +10889,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10701,10 +10941,10 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10753,10 +10993,10 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10809,10 +11049,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10863,14 +11103,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N62" s="7" t="inlineStr">
+      <c r="N62" s="10" t="inlineStr">
         <is>
           <t>(전일) 암라이즈(시멘트·콘크리트 건자재): 2분기 EPS 원가인플레로 부진, EBITDA 가이던스 하향</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10919,10 +11159,10 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10971,15 +11211,15 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11027,10 +11267,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="7" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11079,15 +11319,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr">
+        <is>
+          <t>루브릭(데이터 백업·사이버복원 SaaS): 보안주 랠리 동반, CSA AI보안 뱅가드 멤버 선정</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11131,10 +11375,10 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11183,10 +11427,10 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" s="7" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11235,10 +11479,10 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="7" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11291,14 +11535,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N70" s="7" t="inlineStr">
+      <c r="N70" s="10" t="inlineStr">
         <is>
           <t>(전일) 제임스하디(파이버시멘트 건축자재): FY27 1분기 EBITDA 가이던스 상회, AZEK 통합 기대</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11347,10 +11591,10 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11399,15 +11643,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="7" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11449,10 +11693,10 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11501,15 +11745,15 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="7" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11553,15 +11797,15 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" s="7" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11605,10 +11849,10 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11657,15 +11901,15 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11709,15 +11953,15 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="7" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11761,10 +12005,10 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11813,10 +12057,10 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11861,15 +12105,15 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11913,10 +12157,10 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11969,15 +12213,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N83" s="7" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr">
+        <is>
+          <t>바이오마린(희귀질환 바이오제약): 8/6 2분기 EPS 서프라이즈·가이던스 상향 여진</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12023,15 +12271,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N84" s="7" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12075,15 +12323,15 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" s="7" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12127,10 +12375,14 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="7" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>게이밍앤레저프로퍼티스(카지노 부동산 리츠): 특별한 뉴스 없음, 리츠 동반 약세(금리 부담 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12177,10 +12429,10 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" s="7" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12233,19 +12485,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N88" s="7" t="inlineStr">
+      <c r="N88" s="10" t="inlineStr">
         <is>
           <t>(전일) 할로자임(약물전달 플랫폼 ENHANZE 로열티): 2분기 서프라이즈·연간 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12289,10 +12541,14 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="7" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>에버코어(M&amp;A 자문 IB): 특별한 뉴스 없음, 2분기 서프라이즈 소화 후 밸류에이션 조정 추정</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12341,10 +12597,10 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" s="7" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12393,15 +12649,15 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" s="7" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12449,15 +12705,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N92" s="7" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12501,7 +12757,7 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="7" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N93"/>
@@ -12607,7 +12863,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12654,15 +12910,15 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12710,15 +12966,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>리크루트(구인 플랫폼 인디드·HR): FY27.3 영업이익 7870억→9450억엔 상향, 1Q 영업이익 66%↑</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12762,10 +13022,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>닌텐도(게임기·소프트, 스위치): 1Q 매출 9.5%↓에도 영업이익 150%↑ 서프라이즈로 강세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12816,14 +13080,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 오츠카홀딩스(제약·헬스케어): 연간 실적·배당 상향, 신장병 신약 임상 호조</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12870,19 +13134,19 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 혼다(자동차): 1분기 순이익 2.3배, 연간 전망 53.8% 상향에 목표주가 동반 상향</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12926,10 +13190,10 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12980,19 +13244,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 브리지스톤(타이어 제조): 상반기 순이익 79%↑ 사상 최대, 상장 이래 최고가 경신</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13034,10 +13298,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13084,14 +13352,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 반다이남코(게임·완구 IP): 1분기 사상 최대 실적, 2분기 누계 가이던스도 상향</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13142,10 +13410,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13192,14 +13460,14 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) LY코퍼레이션(야후재팬·라인): 1분기 사상 최대 실적 + 1500억엔 자사주매입</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13246,19 +13514,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) 카지마(종합건설): 특별한 뉴스 없음, 건설 섹터 동반 조정 추정</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13302,10 +13570,10 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13354,10 +13622,10 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13404,10 +13672,14 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>올림푸스(내시경 등 의료기기): 1Q 매출 16.4%↑·영업이익 74.4%↑·순이익 2.1배로 예상 상회</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13454,19 +13726,19 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>(전일) 오바야시구미(종합건설): 1분기 영업이익 98%↑에도 가이던스 유지, 차익실현 매물</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13508,10 +13780,14 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>도쿄가스(도시가스): 특별한 뉴스 없음, 7/30 1Q 경상이익 13.3%↓ 소화 후 전력·가스 섹터 조정 추정</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13564,14 +13840,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>(전일) 도레이(첨단소재·탄소섬유): 1분기 순이익 92.6%↑, 상반기 이익전망 13% 상향</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13618,19 +13894,19 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>(전일) 산리오(헬로키티 캐릭터 IP): 5기 연속 최고실적, 아시아 매출 급증에 신고가</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13678,15 +13954,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>야마하모터(이륜차·마린엔진): 8/4 FY26.12 순이익 1000억→1700억엔 상향 후 상장래 최고가 경신</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13728,15 +14008,15 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13782,15 +14062,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>젠쇼(스키야 등 외식체인): FY26.3 증수증익, 8/7 FY27.3 실적전망 상향 발표 후 상승 지속</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13838,10 +14122,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13888,7 +14172,11 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>니토리(가구·생활용품 SPA): 1Q 영업이익 365억엔으로 소폭 감익이나 시장예상 상회, 이익률 개선 호감</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N25"/>
@@ -13994,12 +14282,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14041,10 +14329,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>메이퇀(중국 최대 배달·로컬서비스 플랫폼): 특별한 뉴스 없음, 보합권에서 52주 고가권 유지</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14095,14 +14387,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 우시앱텍(신약 위탁연구 CRO): 상반기 순이익 29% 증가 서프라이즈, CXO 급등 주도</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14155,14 +14447,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 레노버(PC·서버 제조): AI서버 수주 210억달러·실적 호조로 신고가 경신</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14211,14 +14503,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 베이진(신약개발 바이오텍): 실적 호조·애널리스트 상향 속 CXO 섹터 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14269,10 +14561,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14323,19 +14615,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 스와이어퍼시픽B(항공·부동산 복합기업): 상반기 순이익 43% 증가 서프라이즈</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14379,15 +14671,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>텐센트뮤직(중국 1위 음원 스트리밍): 화처잉스와 전략 제휴 소식, 밸류 매력에 반등</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14435,15 +14731,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>SITC인터내셔널(아시아 역내 컨테이너 해운): 특별한 뉴스 없음, 해운 수급 흐름 추정</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14485,10 +14785,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>츠펑지룽금광H(금광 채굴): 금값 랠리 이후 차익실현 매물, 고가권 등락</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14541,19 +14845,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 캉룽화청(신약 위탁연구 CRO): 우시앱텍 실적 서프라이즈로 CXO 섹터 동반 급등</t>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>캉룽화청(신약 위탁연구 CRO): CXO 섹터 랠리 지속·실적 호조로 목표주가 상향 잇따름(개별 신규 촉매는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14595,7 +14899,11 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>중국황금국제자원(금·구리 광산): 금값 랠리 이후 차익실현 매물 출회</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N12"/>
@@ -14701,7 +15009,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14750,19 +15058,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 베이진A(바이오 신약): 8월 5일 발표 상반기 실적 서프라이즈, 주력 신약 매출 29%↑</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14806,15 +15114,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>코스코시핑홀딩스(중국 최대 컨테이너 해운): SCFI 8월초 3200선 회복·미서안 운임 급등, 당일은 소폭 조정</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14856,10 +15168,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>중진황금(국영 금 채굴): 금값 고점권 강세로 7월 이후 10%대 반등, 금광주 랠리 동참</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14910,19 +15226,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 루이터커지(적외선 열영상 센서): 특별한 뉴스 없음, 실적장세 이후 수급 흐름 추정</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14964,10 +15280,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>츠펑지룽금광A(금광 개발): 8/5~6 8%대 급등 등 금광주 랠리 주도, 당일은 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15020,19 +15340,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 캉룽화청A(신약 위탁개발 CXO): 상반기 중국 기술수출 2배 급증·수주잔고 25%↑</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15074,7 +15394,11 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>산진국제황금(금광 개발): 금값 온스당 4300~4400달러대 고공권에 금광주 랠리 동참, 숨고르기</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N8"/>
